--- a/gBanque/src/main/resources/lignes_fonctionnelles_specifiques_data.xlsx
+++ b/gBanque/src/main/resources/lignes_fonctionnelles_specifiques_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B6725F-C4C3-4890-9441-CB9DF25A691E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C335DFA-C141-40F4-93E4-0A50C43675F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="31">
-  <si>
-    <t>banqueName</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>natureLibelle</t>
   </si>
@@ -40,46 +37,13 @@
     <t>dateFin</t>
   </si>
   <si>
-    <t>AWB</t>
-  </si>
-  <si>
-    <t>BMCE</t>
-  </si>
-  <si>
     <t>Préfinancement</t>
   </si>
   <si>
     <t>Droit constaté</t>
   </si>
   <si>
-    <t>01/01/2025</t>
-  </si>
-  <si>
-    <t>31/12/2025</t>
-  </si>
-  <si>
     <t>Numero de marche</t>
-  </si>
-  <si>
-    <t>BMCI</t>
-  </si>
-  <si>
-    <t>CDM</t>
-  </si>
-  <si>
-    <t>SGMB</t>
-  </si>
-  <si>
-    <t>BPMG</t>
-  </si>
-  <si>
-    <t>BP</t>
-  </si>
-  <si>
-    <t>CIH</t>
-  </si>
-  <si>
-    <t>FINEA</t>
   </si>
   <si>
     <t xml:space="preserve">MAR-0001	</t>
@@ -119,7 +83,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +97,25 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -182,14 +168,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,17 +487,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" customWidth="1"/>
-    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -514,431 +506,374 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>100000</v>
+      </c>
+      <c r="C2">
+        <v>0.05</v>
+      </c>
+      <c r="D2" s="4">
+        <v>45658</v>
+      </c>
+      <c r="E2" s="5">
+        <v>46022</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
-        <v>100000</v>
-      </c>
-      <c r="D2">
-        <v>0.05</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>200000</v>
+      </c>
+      <c r="C3">
+        <v>0.03</v>
+      </c>
+      <c r="D3" s="4">
+        <v>45658</v>
+      </c>
+      <c r="E3" s="5">
+        <v>46022</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>150000</v>
+      </c>
+      <c r="C4">
+        <v>0.04</v>
+      </c>
+      <c r="D4" s="4">
+        <v>45658</v>
+      </c>
+      <c r="E4" s="5">
+        <v>46022</v>
+      </c>
+      <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="C3">
-        <v>200000</v>
-      </c>
-      <c r="D3">
-        <v>0.03</v>
-      </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>180000</v>
+      </c>
+      <c r="C5">
+        <v>0.02</v>
+      </c>
+      <c r="D5" s="4">
+        <v>45658</v>
+      </c>
+      <c r="E5" s="5">
+        <v>46022</v>
+      </c>
+      <c r="F5" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
         <v>150000</v>
       </c>
-      <c r="D4">
+      <c r="C6">
         <v>0.04</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>180000</v>
-      </c>
-      <c r="D5">
-        <v>0.02</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>150000</v>
-      </c>
-      <c r="D6">
-        <v>0.04</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
+      <c r="D6" s="4">
+        <v>45658</v>
+      </c>
+      <c r="E6" s="5">
+        <v>46022</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>180000</v>
+      </c>
+      <c r="C7">
+        <v>0.02</v>
+      </c>
+      <c r="D7" s="4">
+        <v>45658</v>
+      </c>
+      <c r="E7" s="5">
+        <v>46022</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>150000</v>
+      </c>
+      <c r="C8">
+        <v>0.04</v>
+      </c>
+      <c r="D8" s="4">
+        <v>45658</v>
+      </c>
+      <c r="E8" s="5">
+        <v>45961</v>
+      </c>
+      <c r="F8" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
         <v>180000</v>
       </c>
-      <c r="D7">
+      <c r="C9">
         <v>0.02</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="D9" s="4">
+        <v>45658</v>
+      </c>
+      <c r="E9" s="5">
+        <v>45961</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>150000</v>
+      </c>
+      <c r="C10">
+        <v>0.04</v>
+      </c>
+      <c r="D10" s="4">
+        <v>45658</v>
+      </c>
+      <c r="E10" s="5">
+        <v>45961</v>
+      </c>
+      <c r="F10" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>180000</v>
+      </c>
+      <c r="C11">
+        <v>0.02</v>
+      </c>
+      <c r="D11" s="4">
+        <v>45292</v>
+      </c>
+      <c r="E11" s="5">
+        <v>45657</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12">
         <v>150000</v>
       </c>
-      <c r="D8">
+      <c r="C12">
         <v>0.04</v>
       </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9">
+      <c r="D12" s="4">
+        <v>45292</v>
+      </c>
+      <c r="E12" s="5">
+        <v>45657</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
         <v>180000</v>
       </c>
-      <c r="D9">
+      <c r="C13">
         <v>0.02</v>
       </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="D13" s="4">
+        <v>45292</v>
+      </c>
+      <c r="E13" s="5">
+        <v>45657</v>
+      </c>
+      <c r="F13" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14">
         <v>150000</v>
       </c>
-      <c r="D10">
+      <c r="C14">
         <v>0.04</v>
       </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11">
+      <c r="D14" s="4">
+        <v>45292</v>
+      </c>
+      <c r="E14" s="5">
+        <v>45657</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15">
         <v>180000</v>
       </c>
-      <c r="D11">
+      <c r="C15">
         <v>0.02</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="D15" s="4">
+        <v>45292</v>
+      </c>
+      <c r="E15" s="5">
+        <v>45657</v>
+      </c>
+      <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16">
         <v>150000</v>
       </c>
-      <c r="D12">
+      <c r="C16">
         <v>0.04</v>
       </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13">
+      <c r="D16" s="4">
+        <v>45292</v>
+      </c>
+      <c r="E16" s="5">
+        <v>45657</v>
+      </c>
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17">
         <v>180000</v>
       </c>
-      <c r="D13">
+      <c r="C17">
         <v>0.02</v>
       </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="D17" s="4">
+        <v>45293</v>
+      </c>
+      <c r="E17" s="5">
+        <v>45658</v>
+      </c>
+      <c r="F17" t="s">
         <v>17</v>
       </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18">
         <v>150000</v>
       </c>
-      <c r="D14">
+      <c r="C18">
         <v>0.04</v>
       </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15">
+      <c r="D18" s="4">
+        <v>45294</v>
+      </c>
+      <c r="E18" s="5">
+        <v>45659</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19">
         <v>180000</v>
       </c>
-      <c r="D15">
+      <c r="C19">
         <v>0.02</v>
       </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="D19" s="4">
+        <v>45295</v>
+      </c>
+      <c r="E19" s="5">
+        <v>45660</v>
+      </c>
+      <c r="F19" t="s">
         <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16">
-        <v>150000</v>
-      </c>
-      <c r="D16">
-        <v>0.04</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17">
-        <v>180000</v>
-      </c>
-      <c r="D17">
-        <v>0.02</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18">
-        <v>150000</v>
-      </c>
-      <c r="D18">
-        <v>0.04</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19">
-        <v>180000</v>
-      </c>
-      <c r="D19">
-        <v>0.02</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
